--- a/2026年大乐透与双色球开奖数据.xlsx
+++ b/2026年大乐透与双色球开奖数据.xlsx
@@ -530,7 +530,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-18 03:40 (GMT+8)</t>
+          <t>2026-10-18 03:59 (GMT+8)</t>
         </is>
       </c>
     </row>

--- a/2026年大乐透与双色球开奖数据.xlsx
+++ b/2026年大乐透与双色球开奖数据.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'大乐透'!$A$1:$L$119</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'双色球'!$A$1:$L$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'双色球'!$A$1:$L$120</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -530,7 +530,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-18 03:59 (GMT+8)</t>
+          <t>2026-10-18 21:55 (GMT+8)</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>118 期（2026001 — 2026118，2026-01-01 — 2026-10-15）</t>
+          <t>119 期（2026001 — 2026119，2026-01-01 — 2026-10-18）</t>
         </is>
       </c>
     </row>
@@ -5700,7 +5700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L119"/>
+  <dimension ref="A1:L120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -10971,8 +10971,52 @@
         </is>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>2026119</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="D120" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="E120" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="F120" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="G120" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="H120" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="I120" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J120" s="5" t="n">
+        <v>139</v>
+      </c>
+      <c r="K120" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="L120" s="5" t="inlineStr">
+        <is>
+          <t>3:3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L119"/>
+  <autoFilter ref="A1:L120"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/2026年大乐透与双色球开奖数据.xlsx
+++ b/2026年大乐透与双色球开奖数据.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="双色球" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'大乐透'!$A$1:$L$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'大乐透'!$A$1:$L$120</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'双色球'!$A$1:$L$120</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -530,7 +530,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-18 21:55 (GMT+8)</t>
+          <t>2026-10-20 00:37 (GMT+8)</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>118 期（26001 — 26118，2026-01-03 — 2026-10-17）</t>
+          <t>119 期（26001 — 26119，2026-01-03 — 2026-10-19）</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L119"/>
+  <dimension ref="A1:L120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -5688,8 +5688,50 @@
         <v>18</v>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>26119</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D120" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E120" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="F120" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="G120" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="H120" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I120" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="J120" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="K120" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="L120" s="5" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L119"/>
+  <autoFilter ref="A1:L120"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/2026年大乐透与双色球开奖数据.xlsx
+++ b/2026年大乐透与双色球开奖数据.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'大乐透'!$A$1:$L$120</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'双色球'!$A$1:$L$120</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'双色球'!$A$1:$L$121</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -530,7 +530,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20 00:37 (GMT+8)</t>
+          <t>2026-10-20 21:55 (GMT+8)</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>119 期（2026001 — 2026119，2026-01-01 — 2026-10-18）</t>
+          <t>120 期（2026001 — 2026120，2026-01-01 — 2026-10-20）</t>
         </is>
       </c>
     </row>
@@ -5742,7 +5742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L120"/>
+  <dimension ref="A1:L121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -11057,8 +11057,52 @@
         </is>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t>2026120</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="D121" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="E121" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="F121" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="G121" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="H121" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="I121" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J121" s="6" t="n">
+        <v>112</v>
+      </c>
+      <c r="K121" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="L121" s="6" t="inlineStr">
+        <is>
+          <t>2:4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L120"/>
+  <autoFilter ref="A1:L121"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/2026年大乐透与双色球开奖数据.xlsx
+++ b/2026年大乐透与双色球开奖数据.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="双色球" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'大乐透'!$A$1:$L$120</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'大乐透'!$A$1:$L$121</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'双色球'!$A$1:$L$121</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -530,7 +530,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55 (GMT+8)</t>
+          <t>2026-10-21 21:55 (GMT+8)</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>119 期（26001 — 26119，2026-01-03 — 2026-10-19）</t>
+          <t>120 期（26001 — 26120，2026-01-03 — 2026-10-21）</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L120"/>
+  <dimension ref="A1:L121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -5730,8 +5730,50 @@
         <v>11</v>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t>26120</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D121" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E121" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F121" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G121" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="H121" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I121" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J121" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="K121" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="L121" s="6" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L120"/>
+  <autoFilter ref="A1:L121"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/2026年大乐透与双色球开奖数据.xlsx
+++ b/2026年大乐透与双色球开奖数据.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'大乐透'!$A$1:$L$121</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'双色球'!$A$1:$L$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'双色球'!$A$1:$L$122</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -530,7 +530,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21 21:55 (GMT+8)</t>
+          <t>2026-10-22 23:50 (GMT+8)</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>120 期（2026001 — 2026120，2026-01-01 — 2026-10-20）</t>
+          <t>121 期（2026001 — 2026121，2026-01-01 — 2026-10-22）</t>
         </is>
       </c>
     </row>
@@ -5784,7 +5784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L121"/>
+  <dimension ref="A1:L122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -11143,8 +11143,52 @@
         </is>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>2026121</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D122" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E122" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="F122" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="G122" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="H122" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="I122" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J122" s="5" t="n">
+        <v>109</v>
+      </c>
+      <c r="K122" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="L122" s="5" t="inlineStr">
+        <is>
+          <t>1:5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L121"/>
+  <autoFilter ref="A1:L122"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/2026年大乐透与双色球开奖数据.xlsx
+++ b/2026年大乐透与双色球开奖数据.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="双色球" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'大乐透'!$A$1:$L$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'大乐透'!$A$1:$L$122</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'双色球'!$A$1:$L$122</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -530,7 +530,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22 23:50 (GMT+8)</t>
+          <t>2026-10-24 21:55 (GMT+8)</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>120 期（26001 — 26120，2026-01-03 — 2026-10-21）</t>
+          <t>121 期（26001 — 26121，2026-01-03 — 2026-10-24）</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L121"/>
+  <dimension ref="A1:L122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -5772,8 +5772,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>26121</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D122" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E122" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="F122" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="G122" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="H122" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I122" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J122" s="5" t="n">
+        <v>82</v>
+      </c>
+      <c r="K122" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="L122" s="5" t="n">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L121"/>
+  <autoFilter ref="A1:L122"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/2026年大乐透与双色球开奖数据.xlsx
+++ b/2026年大乐透与双色球开奖数据.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'大乐透'!$A$1:$L$122</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'双色球'!$A$1:$L$122</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'双色球'!$A$1:$L$123</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -530,7 +530,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24 21:55 (GMT+8)</t>
+          <t>2026-10-26 20:46 (GMT+8)</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>121 期（2026001 — 2026121，2026-01-01 — 2026-10-22）</t>
+          <t>122 期（2026001 — 2026122，2026-01-01 — 2026-10-25）</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L122"/>
+  <dimension ref="A1:L123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -11229,8 +11229,52 @@
         </is>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>2026122</t>
+        </is>
+      </c>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D123" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E123" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F123" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G123" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="H123" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I123" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="J123" s="6" t="n">
+        <v>73</v>
+      </c>
+      <c r="K123" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="L123" s="6" t="inlineStr">
+        <is>
+          <t>3:3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L122"/>
+  <autoFilter ref="A1:L123"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/2026年大乐透与双色球开奖数据.xlsx
+++ b/2026年大乐透与双色球开奖数据.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="双色球" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'大乐透'!$A$1:$L$122</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'大乐透'!$A$1:$L$123</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'双色球'!$A$1:$L$123</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -530,7 +530,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-26 20:46 (GMT+8)</t>
+          <t>2026-10-26 21:55 (GMT+8)</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>121 期（26001 — 26121，2026-01-03 — 2026-10-24）</t>
+          <t>122 期（26001 — 26122，2026-01-03 — 2026-10-26）</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L122"/>
+  <dimension ref="A1:L123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -5814,8 +5814,50 @@
         <v>9</v>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>26122</t>
+        </is>
+      </c>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D123" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="E123" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="F123" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="G123" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="H123" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I123" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="J123" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="K123" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="L123" s="6" t="n">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L122"/>
+  <autoFilter ref="A1:L123"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/2026年大乐透与双色球开奖数据.xlsx
+++ b/2026年大乐透与双色球开奖数据.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="双色球" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'大乐透'!$A$1:$L$123</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'双色球'!$A$1:$L$123</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'大乐透'!$A$1:$L$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'双色球'!$A$1:$L$124</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -530,7 +530,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-26 21:55 (GMT+8)</t>
+          <t>2026-10-28 21:55 (GMT+8)</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>122 期（26001 — 26122，2026-01-03 — 2026-10-26）</t>
+          <t>123 期（26001 — 26123，2026-01-03 — 2026-10-28）</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>122 期（2026001 — 2026122，2026-01-01 — 2026-10-25）</t>
+          <t>123 期（2026001 — 2026123，2026-01-01 — 2026-10-27）</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L123"/>
+  <dimension ref="A1:L124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -5856,8 +5856,50 @@
         <v>14</v>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>26123</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="D124" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="E124" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="F124" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="G124" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="H124" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="I124" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="J124" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="K124" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L124" s="5" t="n">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L123"/>
+  <autoFilter ref="A1:L124"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5868,7 +5910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L123"/>
+  <dimension ref="A1:L124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -11315,8 +11357,52 @@
         </is>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>2026123</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D124" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E124" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="F124" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="G124" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="H124" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="I124" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="J124" s="5" t="n">
+        <v>106</v>
+      </c>
+      <c r="K124" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="L124" s="5" t="inlineStr">
+        <is>
+          <t>2:4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L123"/>
+  <autoFilter ref="A1:L124"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/2026年大乐透与双色球开奖数据.xlsx
+++ b/2026年大乐透与双色球开奖数据.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'大乐透'!$A$1:$L$124</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'双色球'!$A$1:$L$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'双色球'!$A$1:$L$125</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -530,7 +530,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-28 21:55 (GMT+8)</t>
+          <t>2026-10-29 21:56 (GMT+8)</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>123 期（2026001 — 2026123，2026-01-01 — 2026-10-27）</t>
+          <t>124 期（2026001 — 2026124，2026-01-01 — 2026-10-29）</t>
         </is>
       </c>
     </row>
@@ -5910,7 +5910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L124"/>
+  <dimension ref="A1:L125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -11401,8 +11401,52 @@
         </is>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>2026124</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D125" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="E125" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="F125" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="G125" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="H125" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="I125" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="J125" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="K125" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="L125" s="6" t="inlineStr">
+        <is>
+          <t>5:1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L124"/>
+  <autoFilter ref="A1:L125"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>